--- a/data/trans_camb/P1410-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1410-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,16</t>
+          <t>-4,91; 0,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,81</t>
+          <t>-4,41; 0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,33</t>
+          <t>-2,24; 2,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,04</t>
+          <t>-3,32; 0,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,06</t>
+          <t>0,1; 5,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,1</t>
+          <t>-0,65; 3,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,48</t>
+          <t>-3,52; -0,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,77</t>
+          <t>-2,06; 1,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,93</t>
+          <t>-1,09; 2,4</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>100,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 9,88</t>
+          <t>-77,24; 5,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 32,58</t>
+          <t>-70,65; 30,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 70,15</t>
+          <t>-34,64; 88,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 893,36</t>
+          <t>-19,28; 902,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 550,83</t>
+          <t>-37,9; 663,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,42; -7,57</t>
+          <t>-77,66; -10,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 67,51</t>
+          <t>-45,12; 65,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 75,92</t>
+          <t>-24,82; 96,55</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,24</t>
+          <t>-3,46; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,88</t>
+          <t>-2,45; 3,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,18</t>
+          <t>-1,69; 3,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,57</t>
+          <t>-2,54; 1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,99</t>
+          <t>-2,09; 1,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,07</t>
+          <t>-2,37; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,23</t>
+          <t>-2,12; 1,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,69</t>
+          <t>-1,41; 1,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,86</t>
+          <t>-1,17; 1,74</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,36%</t>
+          <t>-20,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 110,84</t>
+          <t>-72,27; 96,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 146,57</t>
+          <t>-54,18; 140,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,02; 151,09</t>
+          <t>-35,03; 144,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 492,24</t>
+          <t>-100,0; 278,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,16; 381,97</t>
+          <t>-81,01; 299,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 200,94</t>
+          <t>-81,84; 163,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,96; 82,86</t>
+          <t>-63,41; 62,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 98,82</t>
+          <t>-47,13; 109,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 112,13</t>
+          <t>-34,2; 109,42</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,49</t>
+          <t>-2,44; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,39</t>
+          <t>-2,91; 2,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,63</t>
+          <t>-1,15; 4,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,89</t>
+          <t>-1,47; 4,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 11,01</t>
+          <t>1,11; 11,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,58</t>
+          <t>0,73; 9,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,43</t>
+          <t>-1,55; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,2</t>
+          <t>-1,16; 3,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,18</t>
+          <t>0,27; 4,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,11%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>230,18%</t>
+          <t>233,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 69,42</t>
+          <t>-39,48; 65,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 71,05</t>
+          <t>-48,98; 57,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,85; 63,05</t>
+          <t>-20,0; 121,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,62; —</t>
+          <t>-53,14; 846,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1589,11</t>
+          <t>-15,28; 1643,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 1285,75</t>
+          <t>-23,11; 1244,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 78,84</t>
+          <t>-30,96; 83,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 100,57</t>
+          <t>-22,96; 106,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 92,73</t>
+          <t>2,84; 158,67</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,55</t>
+          <t>-2,95; 0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,48</t>
+          <t>-3,17; 0,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,41</t>
+          <t>-1,59; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,18</t>
+          <t>-3,19; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,87</t>
+          <t>-2,52; 1,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,02</t>
+          <t>-3,01; 0,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,05</t>
+          <t>-2,75; -0,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,07</t>
+          <t>-2,45; 0,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,57</t>
+          <t>-1,67; 0,88</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,7%</t>
+          <t>-29,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,36%</t>
+          <t>-7,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 9,9</t>
+          <t>-45,27; 11,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 9,95</t>
+          <t>-47,26; 5,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 50,64</t>
+          <t>-24,47; 41,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 11,39</t>
+          <t>-71,04; 18,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 34,4</t>
+          <t>-57,61; 43,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,29; -0,0</t>
+          <t>-62,13; 12,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,71; -0,76</t>
+          <t>-48,88; -1,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 1,93</t>
+          <t>-43,79; 3,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 13,53</t>
+          <t>-30,12; 21,35</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,21</t>
+          <t>-3,71; 2,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,93</t>
+          <t>-3,91; 1,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,76</t>
+          <t>-2,27; 3,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,5</t>
+          <t>-1,05; 4,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,9</t>
+          <t>-3,23; 1,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-1,06; 3,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,98</t>
+          <t>-1,27; 2,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,0</t>
+          <t>-2,55; 0,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,77</t>
+          <t>-0,72; 2,9</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 69,3</t>
+          <t>-52,86; 66,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 58,42</t>
+          <t>-55,05; 54,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 131,16</t>
+          <t>-30,58; 106,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 129,67</t>
+          <t>-16,76; 117,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 56,26</t>
+          <t>-50,42; 43,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 69,88</t>
+          <t>-16,1; 97,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 73,56</t>
+          <t>-20,65; 70,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 27,45</t>
+          <t>-41,84; 26,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 69,53</t>
+          <t>-11,02; 73,13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>-0,17; 4,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,38</t>
+          <t>-0,62; 1,47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 9,64</t>
+          <t>-0,18; 8,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,95</t>
+          <t>-0,83; 2,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,19</t>
+          <t>-0,12; 4,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,01</t>
+          <t>0,12; 3,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,76</t>
+          <t>-0,39; 2,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,1</t>
+          <t>-0,17; 3,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,6</t>
+          <t>0,41; 3,77</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>627,58%</t>
+          <t>536,44%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 75,5</t>
+          <t>-15,13; 71,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 105,93</t>
+          <t>-2,14; 103,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,06; 103,1</t>
+          <t>1,16; 96,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 86,88</t>
+          <t>-9,94; 82,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 90,44</t>
+          <t>-4,39; 97,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2,54; 104,94</t>
+          <t>8,76; 118,7</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,29</t>
+          <t>-1,79; 0,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,17</t>
+          <t>-1,95; 0,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,67</t>
+          <t>-0,32; 1,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,36</t>
+          <t>-0,58; 1,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,73</t>
+          <t>-0,2; 1,84</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,22</t>
+          <t>-0,24; 1,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,51</t>
+          <t>-0,82; 0,54</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,66</t>
+          <t>-0,7; 0,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,14</t>
+          <t>0,11; 1,45</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,53; 7,5</t>
+          <t>-34,33; 5,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 4,32</t>
+          <t>-36,59; 4,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 38,93</t>
+          <t>-6,1; 45,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 41,35</t>
+          <t>-13,86; 38,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 51,99</t>
+          <t>-4,82; 57,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 36,58</t>
+          <t>-5,86; 49,18</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 13,75</t>
+          <t>-18,34; 14,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 17,45</t>
+          <t>-15,55; 17,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 29,06</t>
+          <t>2,15; 37,61</t>
         </is>
       </c>
     </row>
